--- a/output/2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Butterworth, Penang</t>
@@ -485,8 +484,6 @@
           <t>Hardware industriale, macchinari, utensili automotive/engineering</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Esistenza confermata su Invest Penang SMEs Directory (fornitore hardware industriale e macchinari dal 1983); sito web e contatti diretti non reperiti pubblicamente.</t>
@@ -494,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -524,7 +521,6 @@
           <t>+604 630 1166</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Confermato da Keysight partner page e Ampliz. Email generica non reperita pubblicamente (solo fax +604 630 1168).</t>
@@ -532,7 +528,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -574,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -584,7 +580,6 @@
           <t>Alloytool (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Perai, Pulau Pinang (24-26 Lorong Nagasari 9, Taman Nagasari, 13600)</t>
@@ -595,8 +590,6 @@
           <t>Fornitura utensili da taglio avanzati (carburo, ceramica, CBN, PCD)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Confermato su jobstore.my e investpenang.gov.my (?p=16865); contatti diretti non reperiti.</t>
@@ -604,7 +597,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -614,7 +607,6 @@
           <t>SKN Industrial Supplies Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Butterworth, Penang (843 &amp; 844 Jalan Permatang Tengah, Taman Perkasa, 13000) - fonte alternativa mybina indica Taman Perindustrian Batu Kawan, indirizzo da riconciliare</t>
@@ -625,8 +617,6 @@
           <t>Forniture industriali/semiconduttori, ricambi, distributore esclusivo di brand internazionali</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Confermato come membro SEMI.org dal 2022 e su mybina.com.my; verificare allineamento col settore 'Utensilerie e Macchine Utensili' (focus prevalente su industria semiconduttori).</t>
@@ -634,7 +624,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -644,7 +634,6 @@
           <t>Textran Industries (Penang) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Bukit Mertajam, Pulau Pinang (No.15 Jalan Industri Impian 1, Taman Industri Impian, 14000)</t>
@@ -655,8 +644,6 @@
           <t>Distributore/stockist fasteners, hardware elettromeccanico generale</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Confermato da sme100.asia e investpenang.gov.my; fondata nel 1998 da Tan Bak Soon e Wong Siew Lee.</t>
@@ -664,7 +651,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +661,6 @@
           <t>Butterworth Motoworks Sdn Bhd</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Butterworth, Penang (indirizzo non confermato)</t>
@@ -685,8 +671,6 @@
           <t>Distributore hardware generale, utensili da taglio, macchinari industriali</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Confermato in Invest Penang LLC/SMEs Directory come 'Distributor... General Hardware, Cutting Tools, Industrial Mac[hinery]'; indirizzo e contatti diretti non reperiti.</t>
@@ -704,7 +688,6 @@
           <t>Cipli Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Kepala Batas, Penang</t>
@@ -715,8 +698,6 @@
           <t>Rivenditore/fornitore hardware industriale e materiali da costruzione (dal 1994)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Confermato da Invest Penang SMEs Directory e fonti aggregate (mybina, penang-traveltips); nota: focus su materiali da costruzione più ampio del solo settore utensilerie/macchine utensili.</t>
@@ -724,7 +705,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -734,7 +715,6 @@
           <t>Numac Machinery Sdn Bhd (filiale Penang)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>HQ Petaling Jaya, Selangor; filiale Penang confermata (indirizzo locale non reperito)</t>
@@ -745,8 +725,6 @@
           <t>Dealer/distributore macchine utensili CNC, lamiera/laser, forni trattamento termico, EDM</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Azienda fondata nel 1985, presente su machinetools.com; filiale Penang confermata da fonti aggregate ma indirizzo locale non reperito.</t>
@@ -754,7 +732,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -764,7 +742,6 @@
           <t>Newline Machine Tool Sdn Bhd (filiale Penang)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Butterworth, Penang (19 Jalan Kapal, Chain Ferry Complex, 12100)</t>
@@ -775,8 +752,6 @@
           <t>Dealer/distributore macchine utensili (associato Makino)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Indirizzo filiale Penang confermato da fonti aggregate collegate a machinetools.com/Makino.</t>
@@ -784,7 +759,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -794,7 +769,6 @@
           <t>Henko / BME Industries (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Bayan Lepas, Penang (D-G-2 &amp; D-1-2, Persiaran Relau, Sungai Ara, 11900)</t>
@@ -805,8 +779,6 @@
           <t>Rappresentante/distributore macchine utensili CNC, sistemi di ispezione, laser welding, equipaggiamento per test materiali</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Indirizzo confermato via machinetools.com; HQ gruppo Henko a Singapore con uffici regionali incluso Penang.</t>
@@ -814,7 +786,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -844,7 +816,6 @@
           <t>+60 3 5614 1254 (HQ Malesia)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Presenza tecnico-commerciale a Penang confermata (oltre Selangor e Johor) via Malaysian-German Chamber of Commerce; è filiale del produttore tedesco che vende prodotto proprio (non multi-brand) - valutare se rientra nel target 'distributore terzo' o va considerata produttore/concorrente.</t>
@@ -852,7 +823,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -882,7 +853,6 @@
           <t>+604 380 1277 / 78</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Confermato via fetch diretto del sito ufficiale ecpneumatic.com.my (Reg. 734353-W). Offre anche servizi di lavorazione meccanica custom come servizio aggiuntivo al core business di distribuzione. Email presente sul sito ma non estratta in chiaro (offuscata), non verificabile con certezza - lasciata vuota.</t>
@@ -890,7 +860,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -932,7 +902,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -942,7 +912,6 @@
           <t>P&amp;P Process &amp; Pneumatics Sdn Bhd</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Penang (indirizzo locale non confermato)</t>
@@ -953,8 +922,6 @@
           <t>Distributore/system integrator automazione, fluid power, strumentazione, machine vision &amp; ID systems</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Presenza confermata in Invest Penang SMEs Directory; indirizzo locale specifico non reperito. Verificare allineamento col settore 'utensilerie e macchine utensili' (focus prevalente su automazione/strumentazione).</t>
@@ -962,7 +929,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
